--- a/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3E39235D-3593-40F4-A72F-6064C72F6EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4042E1F6-B48B-41C5-A667-0A3CED5AC5DD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF29F99-14D0-464F-A2DF-6ABDA197F981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Faculty ID</t>
   </si>
@@ -43,16 +43,22 @@
     <t>Saturday</t>
   </si>
   <si>
-    <t>3,4</t>
-  </si>
-  <si>
     <t>5,6</t>
   </si>
   <si>
-    <t>7,8</t>
-  </si>
-  <si>
-    <t>6,7</t>
+    <t>1,2,3,4,5,6,</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>1,2,3,4,7</t>
+  </si>
+  <si>
+    <t>6,7,5</t>
+  </si>
+  <si>
+    <t>5,6,7,1,2,3</t>
   </si>
 </sst>
 </file>
@@ -416,9 +422,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,24 +447,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF29F99-14D0-464F-A2DF-6ABDA197F981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -422,9 +422,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>

--- a/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/faculty-availability-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF29F99-14D0-464F-A2DF-6ABDA197F981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724CA75-D5DF-4AB4-8F73-4B34E9355C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -422,9 +422,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,9 +447,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
